--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto.xlsx
@@ -7409,7 +7409,7 @@
         <v>54.66473005137694</v>
       </c>
       <c r="C415">
-        <v>48.95660496627272</v>
+        <v>48.95660496627271</v>
       </c>
       <c r="D415">
         <v>59.77190773689857</v>
